--- a/Result/profitability/6139.xlsx
+++ b/Result/profitability/6139.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.73</v>
       </c>
       <c r="M2" t="n">
-        <v>6.34125</v>
+        <v>7.8575</v>
       </c>
       <c r="N2" t="n">
-        <v>14.81</v>
+        <v>16.01375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>5.8975</v>
+        <v>7.24125</v>
       </c>
       <c r="N3" t="n">
-        <v>15.8</v>
+        <v>15.76375</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.54</v>
       </c>
       <c r="M4" t="n">
-        <v>5.25125</v>
+        <v>6.83375</v>
       </c>
       <c r="N4" t="n">
-        <v>13.73125</v>
+        <v>14.90625</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.72</v>
       </c>
       <c r="M5" t="n">
-        <v>4.86625</v>
+        <v>6.565</v>
       </c>
       <c r="N5" t="n">
-        <v>13.6</v>
+        <v>15.05625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.44</v>
       </c>
       <c r="M6" t="n">
-        <v>4.5625</v>
+        <v>5.29</v>
       </c>
       <c r="N6" t="n">
-        <v>13.89625</v>
+        <v>14.3075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.09</v>
       </c>
       <c r="M7" t="n">
-        <v>3.243749999999999</v>
+        <v>3.651250000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>12.89375</v>
+        <v>13.10625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.4</v>
       </c>
       <c r="M8" t="n">
-        <v>1.64375</v>
+        <v>2.52</v>
       </c>
       <c r="N8" t="n">
-        <v>12.38125</v>
+        <v>12.7025</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>0.41</v>
       </c>
       <c r="M9" t="n">
-        <v>0.51375</v>
+        <v>0.5137500000000005</v>
       </c>
       <c r="N9" t="n">
         <v>11.89</v>
@@ -1645,7 +1645,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4925</v>
+        <v>0.4925000000000005</v>
       </c>
       <c r="N10" t="n">
         <v>13.04625</v>
@@ -1772,7 +1772,7 @@
         <v>0.52</v>
       </c>
       <c r="M11" t="n">
-        <v>0.46</v>
+        <v>0.4600000000000004</v>
       </c>
       <c r="N11" t="n">
         <v>11.87</v>
@@ -1899,7 +1899,7 @@
         <v>1.03</v>
       </c>
       <c r="M12" t="n">
-        <v>0.52125</v>
+        <v>0.5212500000000004</v>
       </c>
       <c r="N12" t="n">
         <v>12.63375</v>
@@ -2026,7 +2026,7 @@
         <v>1.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.57375</v>
+        <v>0.5737500000000004</v>
       </c>
       <c r="N13" t="n">
         <v>13.75375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>25636</v>
+      </c>
+      <c r="D75" t="n">
+        <v>20175</v>
+      </c>
+      <c r="E75" t="n">
+        <v>5461</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="G75" t="n">
+        <v>4862</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>18.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1293</v>
+      </c>
+      <c r="J75" t="n">
+        <v>6155</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3877</v>
+      </c>
+      <c r="L75" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>8.307500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.55625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>7.010000000000002</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.7417989417989421</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1372130272290444</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>13.59</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>4.735191637630662</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>11.65</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.207253886010363</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
